--- a/peach-bot/webform/임가네_대량주문_양식.xlsx
+++ b/peach-bot/webform/임가네_대량주문_양식.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,11 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00E0673F"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -50,12 +55,17 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBE7DF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -94,23 +104,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -479,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -504,605 +517,800 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>■ 보내는 분 (한 번만 입력)</t>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>★ 작성을 마치면 이 파일을 그대로  qrilli0701@gmail.com  으로 보내주세요 ★</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>■ 보내는 분 (한 번만 입력)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
           <t>성함</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>연락처</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="D6" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>■ 받는 분들 (한 줄에 한 명씩, 필요한 만큼 아래로 계속 추가하세요)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>받는사람</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>연락처(- 없이 11자리)</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>수량(박스)</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>주소</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>요청사항(선택)</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>← 예시 행입니다. 지우고 쓰셔도 되고, 아래부터 채우셔도 됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>김복숭</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>01012345678</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>서울시 강남구 테헤란로 1 101동 1001호</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>딱딱한 걸로</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>김복숭</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>01012345678</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>서울시 강남구 테헤란로 1 101동 1001호</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>딱딱한 걸로</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="n">
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="n">
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="n">
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="n">
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="n">
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="n">
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="n">
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="n">
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="n">
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="n">
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n">
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="n">
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="n">
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="n">
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="n">
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="n">
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="n">
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="n">
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="n">
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="n">
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="n">
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="n">
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="n">
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="n">
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="n">
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="n">
         <v>31</v>
       </c>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="n">
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="n">
         <v>32</v>
       </c>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="n">
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="n">
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="n">
         <v>34</v>
       </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="n">
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="n">
         <v>35</v>
       </c>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n">
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="7" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="n">
         <v>36</v>
       </c>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="n">
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="n">
         <v>37</v>
       </c>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="n">
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="7" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="n">
         <v>38</v>
       </c>
-      <c r="B46" s="5" t="n"/>
-      <c r="C46" s="5" t="n"/>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="n">
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="n">
         <v>39</v>
       </c>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="5" t="n"/>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="n">
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="7" t="n"/>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="6" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="B48" s="5" t="n"/>
-      <c r="C48" s="5" t="n"/>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="n">
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="n">
         <v>41</v>
       </c>
-      <c r="B49" s="5" t="n"/>
-      <c r="C49" s="5" t="n"/>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="n">
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="7" t="n"/>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="6" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="n">
         <v>42</v>
       </c>
-      <c r="B50" s="5" t="n"/>
-      <c r="C50" s="5" t="n"/>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="n">
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="n">
         <v>43</v>
       </c>
-      <c r="B51" s="5" t="n"/>
-      <c r="C51" s="5" t="n"/>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="n">
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="6" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="n">
         <v>44</v>
       </c>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="n">
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="7" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="n">
         <v>45</v>
       </c>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="n">
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="7" t="n"/>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="6" t="n"/>
+      <c r="F54" s="6" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="n">
         <v>46</v>
       </c>
-      <c r="B54" s="5" t="n"/>
-      <c r="C54" s="5" t="n"/>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="n">
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="7" t="n"/>
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="6" t="n"/>
+      <c r="F55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="n">
         <v>47</v>
       </c>
-      <c r="B55" s="5" t="n"/>
-      <c r="C55" s="5" t="n"/>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="10" t="n">
+      <c r="B56" s="6" t="n"/>
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="6" t="n"/>
+      <c r="E56" s="6" t="n"/>
+      <c r="F56" s="6" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="n">
         <v>48</v>
       </c>
-      <c r="B56" s="5" t="n"/>
-      <c r="C56" s="5" t="n"/>
-      <c r="D56" s="5" t="n"/>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="n">
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="7" t="n"/>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="6" t="n"/>
+      <c r="F57" s="6" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="n">
         <v>49</v>
       </c>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="5" t="n"/>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="n">
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="7" t="n"/>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="6" t="n"/>
+      <c r="F58" s="6" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="B58" s="5" t="n"/>
-      <c r="C58" s="5" t="n"/>
-      <c r="D58" s="5" t="n"/>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="10" t="n">
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="6" t="n"/>
+      <c r="E59" s="6" t="n"/>
+      <c r="F59" s="6" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="n">
         <v>51</v>
       </c>
-      <c r="B59" s="5" t="n"/>
-      <c r="C59" s="5" t="n"/>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="n"/>
+      <c r="B60" s="6" t="n"/>
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="6" t="n"/>
+      <c r="E60" s="6" t="n"/>
+      <c r="F60" s="6" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="7" t="n"/>
+      <c r="D61" s="6" t="n"/>
+      <c r="E61" s="6" t="n"/>
+      <c r="F61" s="6" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="n">
+        <v>53</v>
+      </c>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="7" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="6" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="n">
+        <v>54</v>
+      </c>
+      <c r="B63" s="6" t="n"/>
+      <c r="C63" s="7" t="n"/>
+      <c r="D63" s="6" t="n"/>
+      <c r="E63" s="6" t="n"/>
+      <c r="F63" s="6" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="7" t="n"/>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="F64" s="6" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="n">
+        <v>56</v>
+      </c>
+      <c r="B65" s="6" t="n"/>
+      <c r="C65" s="7" t="n"/>
+      <c r="D65" s="6" t="n"/>
+      <c r="E65" s="6" t="n"/>
+      <c r="F65" s="6" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="n">
+        <v>57</v>
+      </c>
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="6" t="n"/>
+      <c r="E66" s="6" t="n"/>
+      <c r="F66" s="6" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="7" t="n"/>
+      <c r="D67" s="6" t="n"/>
+      <c r="E67" s="6" t="n"/>
+      <c r="F67" s="6" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="n">
+        <v>59</v>
+      </c>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="7" t="n"/>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="6" t="n"/>
+      <c r="F68" s="6" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="7" t="n"/>
+      <c r="D69" s="6" t="n"/>
+      <c r="E69" s="6" t="n"/>
+      <c r="F69" s="6" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="7" t="n"/>
+      <c r="D70" s="6" t="n"/>
+      <c r="E70" s="6" t="n"/>
+      <c r="F70" s="6" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="n">
+        <v>62</v>
+      </c>
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="6" t="n"/>
+      <c r="E71" s="6" t="n"/>
+      <c r="F71" s="6" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="n">
+        <v>63</v>
+      </c>
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="7" t="n"/>
+      <c r="D72" s="6" t="n"/>
+      <c r="E72" s="6" t="n"/>
+      <c r="F72" s="6" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="7" t="n"/>
+      <c r="D73" s="6" t="n"/>
+      <c r="E73" s="6" t="n"/>
+      <c r="F73" s="6" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="n">
+        <v>65</v>
+      </c>
+      <c r="B74" s="6" t="n"/>
+      <c r="C74" s="7" t="n"/>
+      <c r="D74" s="6" t="n"/>
+      <c r="E74" s="6" t="n"/>
+      <c r="F74" s="6" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="n">
+        <v>66</v>
+      </c>
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="7" t="n"/>
+      <c r="D75" s="6" t="n"/>
+      <c r="E75" s="6" t="n"/>
+      <c r="F75" s="6" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="n">
+        <v>67</v>
+      </c>
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="7" t="n"/>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="6" t="n"/>
+      <c r="F76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="n">
+        <v>68</v>
+      </c>
+      <c r="B77" s="6" t="n"/>
+      <c r="C77" s="7" t="n"/>
+      <c r="D77" s="6" t="n"/>
+      <c r="E77" s="6" t="n"/>
+      <c r="F77" s="6" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="n">
+        <v>69</v>
+      </c>
+      <c r="B78" s="6" t="n"/>
+      <c r="C78" s="7" t="n"/>
+      <c r="D78" s="6" t="n"/>
+      <c r="E78" s="6" t="n"/>
+      <c r="F78" s="6" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="7" t="n"/>
+      <c r="D79" s="6" t="n"/>
+      <c r="E79" s="6" t="n"/>
+      <c r="F79" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="H9"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/peach-bot/webform/임가네_대량주문_양식.xlsx
+++ b/peach-bot/webform/임가네_대량주문_양식.xlsx
@@ -520,7 +520,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>★ 작성을 마치면 이 파일을 그대로  qrilli0701@gmail.com  으로 보내주세요 ★</t>
+          <t>★ 작성을 마치면 이 파일을 그대로  qrilli0701+peach@gmail.com  으로 보내주세요 ★</t>
         </is>
       </c>
     </row>

--- a/peach-bot/webform/임가네_대량주문_양식.xlsx
+++ b/peach-bot/webform/임가네_대량주문_양식.xlsx
@@ -590,8 +590,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n">
-        <v>1</v>
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>예시</t>
+        </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
@@ -619,7 +621,7 @@
     </row>
     <row r="11">
       <c r="A11" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" s="6" t="n"/>
       <c r="C11" s="7" t="n"/>
@@ -629,7 +631,7 @@
     </row>
     <row r="12">
       <c r="A12" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="7" t="n"/>
@@ -639,7 +641,7 @@
     </row>
     <row r="13">
       <c r="A13" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="7" t="n"/>
@@ -649,7 +651,7 @@
     </row>
     <row r="14">
       <c r="A14" s="13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="7" t="n"/>
@@ -659,7 +661,7 @@
     </row>
     <row r="15">
       <c r="A15" s="13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="7" t="n"/>
@@ -669,7 +671,7 @@
     </row>
     <row r="16">
       <c r="A16" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -679,7 +681,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="7" t="n"/>
@@ -689,7 +691,7 @@
     </row>
     <row r="18">
       <c r="A18" s="13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="7" t="n"/>
@@ -699,7 +701,7 @@
     </row>
     <row r="19">
       <c r="A19" s="13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="7" t="n"/>
@@ -709,7 +711,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="7" t="n"/>
@@ -719,7 +721,7 @@
     </row>
     <row r="21">
       <c r="A21" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="7" t="n"/>
@@ -729,7 +731,7 @@
     </row>
     <row r="22">
       <c r="A22" s="13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="7" t="n"/>
@@ -739,7 +741,7 @@
     </row>
     <row r="23">
       <c r="A23" s="13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="7" t="n"/>
@@ -749,7 +751,7 @@
     </row>
     <row r="24">
       <c r="A24" s="13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B24" s="6" t="n"/>
       <c r="C24" s="7" t="n"/>
@@ -759,7 +761,7 @@
     </row>
     <row r="25">
       <c r="A25" s="13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="7" t="n"/>
@@ -769,7 +771,7 @@
     </row>
     <row r="26">
       <c r="A26" s="13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B26" s="6" t="n"/>
       <c r="C26" s="7" t="n"/>
@@ -779,7 +781,7 @@
     </row>
     <row r="27">
       <c r="A27" s="13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" s="6" t="n"/>
       <c r="C27" s="7" t="n"/>
@@ -789,7 +791,7 @@
     </row>
     <row r="28">
       <c r="A28" s="13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B28" s="6" t="n"/>
       <c r="C28" s="7" t="n"/>
@@ -799,7 +801,7 @@
     </row>
     <row r="29">
       <c r="A29" s="13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B29" s="6" t="n"/>
       <c r="C29" s="7" t="n"/>
@@ -809,7 +811,7 @@
     </row>
     <row r="30">
       <c r="A30" s="13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B30" s="6" t="n"/>
       <c r="C30" s="7" t="n"/>
@@ -819,7 +821,7 @@
     </row>
     <row r="31">
       <c r="A31" s="13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B31" s="6" t="n"/>
       <c r="C31" s="7" t="n"/>
@@ -829,7 +831,7 @@
     </row>
     <row r="32">
       <c r="A32" s="13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B32" s="6" t="n"/>
       <c r="C32" s="7" t="n"/>
@@ -839,7 +841,7 @@
     </row>
     <row r="33">
       <c r="A33" s="13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B33" s="6" t="n"/>
       <c r="C33" s="7" t="n"/>
@@ -849,7 +851,7 @@
     </row>
     <row r="34">
       <c r="A34" s="13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B34" s="6" t="n"/>
       <c r="C34" s="7" t="n"/>
@@ -859,7 +861,7 @@
     </row>
     <row r="35">
       <c r="A35" s="13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B35" s="6" t="n"/>
       <c r="C35" s="7" t="n"/>
@@ -869,7 +871,7 @@
     </row>
     <row r="36">
       <c r="A36" s="13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B36" s="6" t="n"/>
       <c r="C36" s="7" t="n"/>
@@ -879,7 +881,7 @@
     </row>
     <row r="37">
       <c r="A37" s="13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B37" s="6" t="n"/>
       <c r="C37" s="7" t="n"/>
@@ -889,7 +891,7 @@
     </row>
     <row r="38">
       <c r="A38" s="13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B38" s="6" t="n"/>
       <c r="C38" s="7" t="n"/>
@@ -899,7 +901,7 @@
     </row>
     <row r="39">
       <c r="A39" s="13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B39" s="6" t="n"/>
       <c r="C39" s="7" t="n"/>
@@ -909,7 +911,7 @@
     </row>
     <row r="40">
       <c r="A40" s="13" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B40" s="6" t="n"/>
       <c r="C40" s="7" t="n"/>
@@ -919,7 +921,7 @@
     </row>
     <row r="41">
       <c r="A41" s="13" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B41" s="6" t="n"/>
       <c r="C41" s="7" t="n"/>
@@ -929,7 +931,7 @@
     </row>
     <row r="42">
       <c r="A42" s="13" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B42" s="6" t="n"/>
       <c r="C42" s="7" t="n"/>
@@ -939,7 +941,7 @@
     </row>
     <row r="43">
       <c r="A43" s="13" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B43" s="6" t="n"/>
       <c r="C43" s="7" t="n"/>
@@ -949,7 +951,7 @@
     </row>
     <row r="44">
       <c r="A44" s="13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B44" s="6" t="n"/>
       <c r="C44" s="7" t="n"/>
@@ -959,7 +961,7 @@
     </row>
     <row r="45">
       <c r="A45" s="13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B45" s="6" t="n"/>
       <c r="C45" s="7" t="n"/>
@@ -969,7 +971,7 @@
     </row>
     <row r="46">
       <c r="A46" s="13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B46" s="6" t="n"/>
       <c r="C46" s="7" t="n"/>
@@ -979,7 +981,7 @@
     </row>
     <row r="47">
       <c r="A47" s="13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B47" s="6" t="n"/>
       <c r="C47" s="7" t="n"/>
@@ -989,7 +991,7 @@
     </row>
     <row r="48">
       <c r="A48" s="13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B48" s="6" t="n"/>
       <c r="C48" s="7" t="n"/>
@@ -999,7 +1001,7 @@
     </row>
     <row r="49">
       <c r="A49" s="13" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B49" s="6" t="n"/>
       <c r="C49" s="7" t="n"/>
@@ -1009,7 +1011,7 @@
     </row>
     <row r="50">
       <c r="A50" s="13" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" s="6" t="n"/>
       <c r="C50" s="7" t="n"/>
@@ -1019,7 +1021,7 @@
     </row>
     <row r="51">
       <c r="A51" s="13" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B51" s="6" t="n"/>
       <c r="C51" s="7" t="n"/>
@@ -1029,7 +1031,7 @@
     </row>
     <row r="52">
       <c r="A52" s="13" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B52" s="6" t="n"/>
       <c r="C52" s="7" t="n"/>
@@ -1039,7 +1041,7 @@
     </row>
     <row r="53">
       <c r="A53" s="13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B53" s="6" t="n"/>
       <c r="C53" s="7" t="n"/>
@@ -1049,7 +1051,7 @@
     </row>
     <row r="54">
       <c r="A54" s="13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B54" s="6" t="n"/>
       <c r="C54" s="7" t="n"/>
@@ -1059,7 +1061,7 @@
     </row>
     <row r="55">
       <c r="A55" s="13" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B55" s="6" t="n"/>
       <c r="C55" s="7" t="n"/>
@@ -1069,7 +1071,7 @@
     </row>
     <row r="56">
       <c r="A56" s="13" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B56" s="6" t="n"/>
       <c r="C56" s="7" t="n"/>
@@ -1079,7 +1081,7 @@
     </row>
     <row r="57">
       <c r="A57" s="13" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B57" s="6" t="n"/>
       <c r="C57" s="7" t="n"/>
@@ -1089,7 +1091,7 @@
     </row>
     <row r="58">
       <c r="A58" s="13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B58" s="6" t="n"/>
       <c r="C58" s="7" t="n"/>
@@ -1099,7 +1101,7 @@
     </row>
     <row r="59">
       <c r="A59" s="13" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B59" s="6" t="n"/>
       <c r="C59" s="7" t="n"/>
@@ -1109,7 +1111,7 @@
     </row>
     <row r="60">
       <c r="A60" s="13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B60" s="6" t="n"/>
       <c r="C60" s="7" t="n"/>
@@ -1119,7 +1121,7 @@
     </row>
     <row r="61">
       <c r="A61" s="13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B61" s="6" t="n"/>
       <c r="C61" s="7" t="n"/>
@@ -1129,7 +1131,7 @@
     </row>
     <row r="62">
       <c r="A62" s="13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B62" s="6" t="n"/>
       <c r="C62" s="7" t="n"/>
@@ -1139,7 +1141,7 @@
     </row>
     <row r="63">
       <c r="A63" s="13" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B63" s="6" t="n"/>
       <c r="C63" s="7" t="n"/>
@@ -1149,7 +1151,7 @@
     </row>
     <row r="64">
       <c r="A64" s="13" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B64" s="6" t="n"/>
       <c r="C64" s="7" t="n"/>
@@ -1159,7 +1161,7 @@
     </row>
     <row r="65">
       <c r="A65" s="13" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B65" s="6" t="n"/>
       <c r="C65" s="7" t="n"/>
@@ -1169,7 +1171,7 @@
     </row>
     <row r="66">
       <c r="A66" s="13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B66" s="6" t="n"/>
       <c r="C66" s="7" t="n"/>
@@ -1179,7 +1181,7 @@
     </row>
     <row r="67">
       <c r="A67" s="13" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B67" s="6" t="n"/>
       <c r="C67" s="7" t="n"/>
@@ -1189,7 +1191,7 @@
     </row>
     <row r="68">
       <c r="A68" s="13" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B68" s="6" t="n"/>
       <c r="C68" s="7" t="n"/>
@@ -1199,7 +1201,7 @@
     </row>
     <row r="69">
       <c r="A69" s="13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B69" s="6" t="n"/>
       <c r="C69" s="7" t="n"/>
@@ -1209,7 +1211,7 @@
     </row>
     <row r="70">
       <c r="A70" s="13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B70" s="6" t="n"/>
       <c r="C70" s="7" t="n"/>
@@ -1219,7 +1221,7 @@
     </row>
     <row r="71">
       <c r="A71" s="13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B71" s="6" t="n"/>
       <c r="C71" s="7" t="n"/>
@@ -1229,7 +1231,7 @@
     </row>
     <row r="72">
       <c r="A72" s="13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B72" s="6" t="n"/>
       <c r="C72" s="7" t="n"/>
@@ -1239,7 +1241,7 @@
     </row>
     <row r="73">
       <c r="A73" s="13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B73" s="6" t="n"/>
       <c r="C73" s="7" t="n"/>
@@ -1249,7 +1251,7 @@
     </row>
     <row r="74">
       <c r="A74" s="13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B74" s="6" t="n"/>
       <c r="C74" s="7" t="n"/>
@@ -1259,7 +1261,7 @@
     </row>
     <row r="75">
       <c r="A75" s="13" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B75" s="6" t="n"/>
       <c r="C75" s="7" t="n"/>
@@ -1269,7 +1271,7 @@
     </row>
     <row r="76">
       <c r="A76" s="13" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B76" s="6" t="n"/>
       <c r="C76" s="7" t="n"/>
@@ -1279,7 +1281,7 @@
     </row>
     <row r="77">
       <c r="A77" s="13" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B77" s="6" t="n"/>
       <c r="C77" s="7" t="n"/>
@@ -1289,7 +1291,7 @@
     </row>
     <row r="78">
       <c r="A78" s="13" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B78" s="6" t="n"/>
       <c r="C78" s="7" t="n"/>
@@ -1299,7 +1301,7 @@
     </row>
     <row r="79">
       <c r="A79" s="13" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B79" s="6" t="n"/>
       <c r="C79" s="7" t="n"/>
